--- a/output/pdf_financials_xlsx/DSG.xlsx
+++ b/output/pdf_financials_xlsx/DSG.xlsx
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2143,13 +2143,13 @@
         <v>17.221</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>13.733</v>
+        <v>13.676</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>21.821</v>
+        <v>21.488</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>27.77</v>
+        <v>27.575</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>31.5</v>
@@ -2271,13 +2271,13 @@
         <v>34.3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>35.128</v>
+        <v>35.071</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46.831</v>
+        <v>46.498</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>57.369</v>
+        <v>57.174</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>65.129</v>
@@ -2335,13 +2335,13 @@
         <v>27.03277822876193</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>23.21836953216915</v>
+        <v>23.18069454175314</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>27.40898981622381</v>
+        <v>27.2140934098092</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>31.01144367624721</v>
+        <v>30.90603428237825</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>31.96060438023545</v>
@@ -2542,37 +2542,37 @@
         <v>118.053</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>37.213</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>38.135</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>35.145</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>27.298</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>44.403</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>133.661</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>213.437</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>276.385</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>320.952</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>236.138</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>356.526</v>
       </c>
     </row>
     <row r="35">
@@ -2674,37 +2674,37 @@
         <v>118.053</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4.639</v>
+        <v>41.852</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>38.135</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>35.145</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>27.298</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>44.403</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>133.661</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>213.437</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>276.385</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>320.952</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>236.138</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>356.526</v>
       </c>
     </row>
     <row r="37">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31521,7 +31521,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -33095,7 +33095,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">

--- a/output/pdf_financials_xlsx/DSG.xlsx
+++ b/output/pdf_financials_xlsx/DSG.xlsx
@@ -2189,61 +2189,61 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6.068</v>
+        <v>3.644</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>7.364</v>
+        <v>5.133</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>8.798999999999999</v>
+        <v>6.929</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.891</v>
+        <v>11.471</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>14.458</v>
+        <v>11.996</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>17.079</v>
+        <v>14.202</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>21.395</v>
+        <v>17.999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>25.01</v>
+        <v>21.715</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>29.599</v>
+        <v>26.222</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>33.629</v>
+        <v>30.001</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>37.578</v>
+        <v>33.477</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>44.723</v>
+        <v>40.179</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>61.522</v>
+        <v>55.485</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>61.662</v>
+        <v>55.905</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>64.22799999999999</v>
+        <v>59.099</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>65.402</v>
+        <v>60.177</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>65.97499999999999</v>
+        <v>60.501</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>74.988</v>
+        <v>69.399</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>87.131</v>
+        <v>81.18300000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2253,61 +2253,61 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>12.834</v>
+        <v>10.41</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>16.095</v>
+        <v>13.864</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15.524</v>
+        <v>13.654</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.824</v>
+        <v>19.404</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>29.848</v>
+        <v>27.386</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.3</v>
+        <v>31.423</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>35.071</v>
+        <v>31.675</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46.498</v>
+        <v>43.203</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>57.174</v>
+        <v>53.797</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>65.129</v>
+        <v>61.501</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>72.32599999999999</v>
+        <v>68.22499999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>84.233</v>
+        <v>79.68899999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>109.557</v>
+        <v>103.52</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>132.031</v>
+        <v>126.274</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>166.838</v>
+        <v>161.709</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>199.13</v>
+        <v>193.905</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>217.127</v>
+        <v>211.653</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>266.621</v>
+        <v>261.032</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>304.221</v>
+        <v>298.273</v>
       </c>
     </row>
     <row r="30">
@@ -2317,61 +2317,61 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>21.7433290978399</v>
+        <v>17.63659466327827</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>24.37011689176912</v>
+        <v>20.99206589546363</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>21.04435527600043</v>
+        <v>18.50938076130572</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>22.00554575245778</v>
+        <v>19.56541467103605</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>26.18475304851303</v>
+        <v>24.02491446618124</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>27.03277822876193</v>
+        <v>24.76533499365557</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>23.18069454175314</v>
+        <v>20.93605827065184</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>27.2140934098092</v>
+        <v>25.28561395294393</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>30.90603428237825</v>
+        <v>29.0805598049656</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.96060438023545</v>
+        <v>30.18024428424911</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>30.46087626716757</v>
+        <v>28.73369581239813</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>30.61114725025529</v>
+        <v>28.95981044514139</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>33.62800077350203</v>
+        <v>31.77497229819117</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>37.86768923662896</v>
+        <v>36.21652938072184</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>39.28465468930278</v>
+        <v>38.07695024606183</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>40.97207076339365</v>
+        <v>39.89699885188492</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>37.89758278047444</v>
+        <v>36.94214486561209</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>40.95560675883257</v>
+        <v>40.09708141321045</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>41.73173368157676</v>
+        <v>40.9158125192046</v>
       </c>
     </row>
     <row r="31">
@@ -7095,61 +7095,61 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>3.644</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>5.133</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>6.929</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>11.471</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>11.996</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>14.202</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>17.999</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>21.715</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>26.222</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>30.001</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>33.477</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>40.179</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>55.485</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>55.905</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>59.099</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>60.177</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>60.501</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>69.399</v>
       </c>
       <c r="T100" s="3" t="n">
-        <v>0</v>
+        <v>81.18300000000001</v>
       </c>
     </row>
     <row r="101">
@@ -8390,46 +8390,46 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.704</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>3.633</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>140.724</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0</v>
+        <v>1.003</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>237.973</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>6.194</v>
       </c>
       <c r="P120" s="3" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R120" s="3" t="n">
-        <v>0</v>
+        <v>9.272</v>
       </c>
       <c r="S120" s="3" t="n">
-        <v>0</v>
+        <v>12.391</v>
       </c>
       <c r="T120" s="3" t="n">
-        <v>0</v>
+        <v>14.104</v>
       </c>
     </row>
     <row r="121">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -22867,7 +22867,11 @@
           <t>Issuance of common shares for cash, net of issuance costs (Note 15)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -24417,7 +24421,11 @@
           <t>Issuance of common shares for cash, net of issuance costs (Note 14)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -26179,7 +26187,11 @@
           <t>Issuance of common shares for cash, net of issuance costs</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -31284,7 +31296,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
